--- a/data/trans_dic/P32D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,75; 24,89</t>
+          <t>8,77; 24,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 26,67</t>
+          <t>8,51; 26,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 22,58</t>
+          <t>10,08; 23,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 16,01</t>
+          <t>5,93; 16,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 16,62</t>
+          <t>5,14; 17,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,11</t>
+          <t>6,48; 13,96</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 13,71</t>
+          <t>6,52; 13,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,1</t>
+          <t>1,75; 7,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 10,08</t>
+          <t>5,38; 10,3</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 11,64</t>
+          <t>5,61; 11,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,85</t>
+          <t>2,88; 7,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 9,19</t>
+          <t>4,84; 9,06</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,15</t>
+          <t>5,8; 12,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,06</t>
+          <t>2,28; 7,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 9,65</t>
+          <t>5,4; 9,75</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,63</t>
+          <t>4,26; 10,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,04; 5,63</t>
+          <t>0,13; 6,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 7,09</t>
+          <t>1,06; 7,38</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,23</t>
+          <t>2,48; 10,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,73</t>
+          <t>0,0; 22,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 10,24</t>
+          <t>2,66; 10,01</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,81; 10,89</t>
+          <t>7,78; 10,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,49</t>
+          <t>2,69; 7,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,91</t>
+          <t>5,67; 8,93</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14866; 42283</t>
+          <t>14896; 41389</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7915; 26897</t>
+          <t>8581; 26880</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27393; 61142</t>
+          <t>27279; 62702</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13816; 36581</t>
+          <t>13553; 36899</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7146; 23646</t>
+          <t>7306; 24206</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23933; 52325</t>
+          <t>24010; 51763</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17890; 38700</t>
+          <t>18393; 39083</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2574; 10706</t>
+          <t>2639; 11211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22833; 43636</t>
+          <t>23317; 44605</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19098; 39948</t>
+          <t>19250; 38588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5099; 14907</t>
+          <t>5471; 14551</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25990; 48990</t>
+          <t>25812; 48270</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15938; 31770</t>
+          <t>15158; 31383</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3339; 10768</t>
+          <t>3053; 10578</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20177; 38130</t>
+          <t>21358; 38530</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8486; 19901</t>
+          <t>7967; 19674</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>113; 15778</t>
+          <t>363; 17279</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5173; 33149</t>
+          <t>4973; 34468</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2275; 10079</t>
+          <t>2443; 10393</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6067</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3269; 12839</t>
+          <t>3334; 12544</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>122651; 171136</t>
+          <t>122231; 171466</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28096; 76684</t>
+          <t>27570; 76004</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>149926; 231208</t>
+          <t>147196; 231696</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32D_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,77; 24,36</t>
+          <t>10,24; 29,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 26,65</t>
+          <t>8,98; 26,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,08; 23,16</t>
+          <t>12,14; 24,89</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,93; 16,15</t>
+          <t>6,71; 17,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,14; 17,02</t>
+          <t>6,09; 16,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,48; 13,96</t>
+          <t>7,6; 15,5</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 13,85</t>
+          <t>6,59; 13,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,43</t>
+          <t>1,84; 7,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,3</t>
+          <t>5,49; 10,45</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,61; 11,24</t>
+          <t>6,08; 12,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,67</t>
+          <t>3,05; 7,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 9,06</t>
+          <t>5,5; 9,61</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,8; 12,0</t>
+          <t>5,7; 11,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,91</t>
+          <t>2,33; 7,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,75</t>
+          <t>5,06; 9,65</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,51</t>
+          <t>4,26; 10,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 6,17</t>
+          <t>2,02; 8,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 7,38</t>
+          <t>4,12; 9,28</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 10,55</t>
+          <t>2,67; 10,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,62</t>
+          <t>0,0; 24,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,01</t>
+          <t>2,79; 11,13</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,91</t>
+          <t>8,12; 11,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 7,42</t>
+          <t>5,63; 9,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,67; 8,93</t>
+          <t>7,65; 10,07</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25643</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>47513</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14896; 41389</t>
+          <t>17023; 48524</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8581; 26880</t>
+          <t>10135; 29703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27279; 62702</t>
+          <t>33886; 69456</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>15972</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>43896</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13553; 36899</t>
+          <t>16630; 43142</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7306; 24206</t>
+          <t>9316; 25919</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24010; 51763</t>
+          <t>30488; 62158</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32309</t>
+          <t>36274</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18393; 39083</t>
+          <t>20615; 41195</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2639; 11211</t>
+          <t>3130; 12227</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23317; 44605</t>
+          <t>26502; 50423</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27589</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>41205</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19250; 38588</t>
+          <t>21511; 42826</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5471; 14551</t>
+          <t>6404; 16388</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25812; 48270</t>
+          <t>31013; 54197</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>23240</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>29951</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15158; 31383</t>
+          <t>15891; 33223</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3053; 10578</t>
+          <t>3421; 11557</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21358; 38530</t>
+          <t>21533; 41102</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>18319</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7967; 19674</t>
+          <t>8737; 21628</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>363; 17279</t>
+          <t>1632; 7128</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4973; 34468</t>
+          <t>11764; 26520</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1738</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>8510</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2443; 10393</t>
+          <t>2882; 11331</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 6067</t>
+          <t>0; 7678</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3334; 12544</t>
+          <t>3876; 15437</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>161482</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>54715</t>
+          <t>64186</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>198824</t>
+          <t>225668</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>122231; 171466</t>
+          <t>135843; 191270</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>27570; 76004</t>
+          <t>50900; 82942</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>147196; 231696</t>
+          <t>197117; 259529</t>
         </is>
       </c>
     </row>
